--- a/product_selector_out/STM32L4x5.xlsx
+++ b/product_selector_out/STM32L4x5.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3783,9 +3783,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="8" t="inlineStr">
@@ -4110,9 +4110,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="8" t="inlineStr">
@@ -4437,9 +4437,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="8" t="inlineStr">
@@ -4764,9 +4764,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="8" t="inlineStr">
@@ -5091,9 +5091,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="8" t="inlineStr">
@@ -5418,9 +5418,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="8" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5612,19 +5612,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L475RE</t>
+          <t>STM32L475VC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5678,19 +5678,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L475VG</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5700,19 +5700,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L475VG</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5744,19 +5744,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5766,19 +5766,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5788,14 +5788,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5817,7 +5817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5832,14 +5832,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5861,12 +5861,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5876,19 +5876,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L475RG</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5898,19 +5898,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L475RG</t>
+          <t>STM32L475RC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5920,27 +5920,159 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>STM32L475RC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L475RC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L475RC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>STM32L475RG</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L475RG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L475RG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L475RG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32L4x5.xlsx
+++ b/product_selector_out/STM32L4x5.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -3643,14 +3643,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -3673,9 +3673,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -3733,9 +3733,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -3970,14 +3970,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -4000,9 +4000,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -4060,9 +4060,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -4297,14 +4297,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -4327,9 +4327,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -4387,9 +4387,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -4624,14 +4624,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -4654,9 +4654,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -4714,9 +4714,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -4951,14 +4951,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -4981,9 +4981,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -5041,9 +5041,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -5278,14 +5278,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -5308,9 +5308,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -5368,9 +5368,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x5.xlsx
+++ b/product_selector_out/STM32L4x5.xlsx
@@ -3733,9 +3733,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -4060,9 +4060,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -4387,9 +4387,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -4714,9 +4714,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -5041,9 +5041,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -5368,9 +5368,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4x5.xlsx
+++ b/product_selector_out/STM32L4x5.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -2955,12 +2987,17 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2981,16 +3018,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3003,6 +3038,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3022,7 +3058,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3045,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3113,6 +3151,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3446,6 +3485,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -3541,6 +3585,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3863,7 +3908,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4190,7 +4240,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4517,7 +4572,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4844,7 +4904,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5171,7 +5236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5498,7 +5568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5506,8 +5581,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
